--- a/PoC/Golden_Annotation_Template.xlsx
+++ b/PoC/Golden_Annotation_Template.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workbook_Info" sheetId="1" r:id="Re42bd4209a0349e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table_Annotation" sheetId="2" r:id="Re50147aedfa44687"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Header_Annotation" sheetId="3" r:id="Rea42e1913d4449d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cell_Truth" sheetId="4" r:id="Rb0623565c63a4a4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workbook_Info" sheetId="1" r:id="R988efed5aa954e8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table_Annotation" sheetId="2" r:id="Rf2f10b50405d4cd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Header_Annotation" sheetId="3" r:id="Rb812f1e8f26c49eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cell_Truth" sheetId="4" r:id="R450a77f1a3d349f9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -134,9 +134,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">二层表头</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">’</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">字段</x:t>
@@ -354,7 +351,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="8">
+  <x:cellXfs count="13">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -376,6 +373,26 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -597,7 +614,7 @@
   <x:sheetFormatPr defaultRowHeight="14"/>
   <x:cols>
     <x:col min="1" max="1" width="9.33203125" customWidth="1"/>
-    <x:col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="11.08203125" customWidth="1"/>
     <x:col min="4" max="4" width="13.08203125" customWidth="1"/>
     <x:col min="5" max="5" width="13.83203125" customWidth="1"/>
@@ -651,6 +668,52 @@
         <x:v>13</x:v>
       </x:c>
     </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>G002</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>Tabs_ISE17933_HK_0807.xlsx</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>Decipher</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>Tab Book PoC</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>Chinese</x:v>
+      </x:c>
+      <x:c r="F3" t="str">
+        <x:v>HK/TW</x:v>
+      </x:c>
+      <x:c r="G3" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>G003</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>Tabs_N+%.xlsx</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>Quantum</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>Tab Book PoC</x:v>
+      </x:c>
+      <x:c r="E4" t="str">
+        <x:v>English</x:v>
+      </x:c>
+      <x:c r="F4" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="G4" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -660,68 +723,84 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="14"/>
   <x:cols>
-    <x:col min="2" max="2" width="11.5" customWidth="1"/>
-    <x:col min="3" max="3" width="11.83203125" customWidth="1"/>
-    <x:col min="19" max="19" width="24" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="24" hidden="0" customWidth="1"/>
-    <x:col min="21" max="21" width="24" hidden="0" customWidth="1"/>
-    <x:col min="22" max="22" width="24" hidden="0" customWidth="1"/>
-    <x:col min="23" max="23" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="18" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="20" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="22" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="12" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="15" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="13" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="10" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="10" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="12" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="13" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="14" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="10" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="10" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="13" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" t="s">
+      <x:c r="A1" s="7" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" t="s">
+      <x:c r="B1" s="7" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C1" t="s">
+      <x:c r="C1" s="7" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D1" t="s">
+      <x:c r="D1" s="7" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E1" t="s">
+      <x:c r="E1" s="7" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F1" t="s">
+      <x:c r="F1" s="7" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G1" t="s">
+      <x:c r="G1" s="7" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H1" t="s">
+      <x:c r="H1" s="7" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I1" t="s">
+      <x:c r="I1" s="7" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="J1" t="s">
+      <x:c r="J1" s="7" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="K1" t="s">
+      <x:c r="K1" s="7" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="L1" t="s">
+      <x:c r="L1" s="7" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="M1" t="s">
+      <x:c r="M1" s="7" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="N1" t="s">
+      <x:c r="N1" s="7" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="O1" t="s">
+      <x:c r="O1" s="7" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="P1" t="s">
+      <x:c r="P1" s="7" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="Q1" t="s">
+      <x:c r="Q1" s="7" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="R1" t="s">
+      <x:c r="R1" s="7" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="S1" s="7" t="str">
@@ -741,82 +820,1475 @@
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="s">
+      <x:c r="A2" s="7" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B2" t="s">
+      <x:c r="B2" s="7" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C2" t="s">
+      <x:c r="C2" s="7" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D2" t="s">
+      <x:c r="D2" s="7" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E2" t="s">
+      <x:c r="E2" s="7" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F2" t="s">
+      <x:c r="F2" s="7" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G2" t="s">
+      <x:c r="G2" s="7" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="H2">
+      <x:c r="H2" s="7">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I2" s="3" t="s">
+      <x:c r="I2" s="8" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="J2">
+      <x:c r="J2" s="7">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K2" s="4" t="s">
+      <x:c r="K2" s="7" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="M2" t="s">
+      <x:c r="L2" s="7"/>
+      <x:c r="M2" s="7" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="N2" t="s">
+      <x:c r="N2" s="7" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="O2" t="s">
+      <x:c r="O2" s="7" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="P2" t="s">
+      <x:c r="P2" s="7" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="Q2" t="s">
+      <x:c r="Q2" s="7" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="R2" t="s">
+      <x:c r="R2" s="7" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="S2" t="str">
+      <x:c r="S2" s="7" t="str">
         <x:v>none</x:v>
       </x:c>
-      <x:c r="T2" t="str">
+      <x:c r="T2" s="7" t="str">
         <x:v>complete</x:v>
       </x:c>
-      <x:c r="U2" t="str">
+      <x:c r="U2" s="7" t="str">
         <x:v>accepted</x:v>
       </x:c>
-      <x:c r="V2" t="n">
+      <x:c r="V2" s="7" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="W2" s="6" t="b">
+      <x:c r="W2" s="9" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="R3" t="s">
+      <x:c r="A3" s="7" t="str">
+        <x:v>G002</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="str">
+        <x:v>G002_T01</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="str">
+        <x:v>Counts</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="str">
+        <x:v>A12:BB18</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="str">
+        <x:v>S1</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="str">
+        <x:v>S1: 請問您的性別是？</x:v>
+      </x:c>
+      <x:c r="G3" s="7" t="str">
+        <x:v>S1: 請問您的性別是？</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="str">
+        <x:v>14:15</x:v>
+      </x:c>
+      <x:c r="J3" s="7" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="K3" s="7" t="str">
+        <x:v>17:18</x:v>
+      </x:c>
+      <x:c r="L3" s="7"/>
+      <x:c r="M3" s="7" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="N3" s="7" t="str">
+        <x:v>cross_tab</x:v>
+      </x:c>
+      <x:c r="O3" s="7" t="str">
+        <x:v>HK/TW</x:v>
+      </x:c>
+      <x:c r="P3" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q3" s="7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="R3" s="7" t="str">
+        <x:v>Initial; no sig in Counts</x:v>
+      </x:c>
+      <x:c r="S3" s="7" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="T3" s="7" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="U3" s="7" t="str">
+        <x:v>accepted</x:v>
+      </x:c>
+      <x:c r="V3" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W3" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="7" t="str">
+        <x:v>G002</x:v>
+      </x:c>
+      <x:c r="B4" s="7" t="str">
+        <x:v>G002_T02</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="str">
+        <x:v>Counts</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="str">
+        <x:v>A21:BB28</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="str">
+        <x:v>S2_HK</x:v>
+      </x:c>
+      <x:c r="F4" s="7" t="str">
+        <x:v>S2_HK: 請選擇您所居住的地區</x:v>
+      </x:c>
+      <x:c r="G4" s="7" t="str">
+        <x:v>S2_HK: 請選擇您所居住的地區</x:v>
+      </x:c>
+      <x:c r="H4" s="7" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I4" s="7" t="str">
+        <x:v>23:24</x:v>
+      </x:c>
+      <x:c r="J4" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K4" s="7" t="str">
+        <x:v>26:28</x:v>
+      </x:c>
+      <x:c r="L4" s="7"/>
+      <x:c r="M4" s="7" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="N4" s="7" t="str">
+        <x:v>cross_tab</x:v>
+      </x:c>
+      <x:c r="O4" s="7" t="str">
+        <x:v>HK/TW</x:v>
+      </x:c>
+      <x:c r="P4" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q4" s="7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="R4" s="7" t="str">
+        <x:v>Initial; no sig in Counts</x:v>
+      </x:c>
+      <x:c r="S4" s="7" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="T4" s="7" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="U4" s="7" t="str">
+        <x:v>accepted</x:v>
+      </x:c>
+      <x:c r="V4" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W4" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="7" t="str">
+        <x:v>G002</x:v>
+      </x:c>
+      <x:c r="B5" s="7" t="str">
+        <x:v>G002_T03</x:v>
+      </x:c>
+      <x:c r="C5" s="7" t="str">
+        <x:v>Counts</x:v>
+      </x:c>
+      <x:c r="D5" s="7" t="str">
+        <x:v>A31:BB38</x:v>
+      </x:c>
+      <x:c r="E5" s="7" t="str">
+        <x:v>S3</x:v>
+      </x:c>
+      <x:c r="F5" s="7" t="str">
+        <x:v>S3: 請選擇您的年齡（周歲）</x:v>
+      </x:c>
+      <x:c r="G5" s="7" t="str">
+        <x:v>S3: 請選擇您的年齡（周歲）</x:v>
+      </x:c>
+      <x:c r="H5" s="7" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="I5" s="7" t="str">
+        <x:v>33:34</x:v>
+      </x:c>
+      <x:c r="J5" s="7" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="K5" s="7" t="str">
+        <x:v>36:38</x:v>
+      </x:c>
+      <x:c r="L5" s="7"/>
+      <x:c r="M5" s="7" t="str">
+        <x:v>mean</x:v>
+      </x:c>
+      <x:c r="N5" s="7" t="str">
+        <x:v>cross_tab</x:v>
+      </x:c>
+      <x:c r="O5" s="7" t="str">
+        <x:v>HK/TW</x:v>
+      </x:c>
+      <x:c r="P5" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q5" s="7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="R5" s="7" t="str">
+        <x:v>Initial; no sig in Counts</x:v>
+      </x:c>
+      <x:c r="S5" s="7" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="T5" s="7" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="U5" s="7" t="str">
+        <x:v>accepted</x:v>
+      </x:c>
+      <x:c r="V5" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W5" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="7" t="str">
+        <x:v>G002</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="str">
+        <x:v>G002_T04</x:v>
+      </x:c>
+      <x:c r="C6" s="7" t="str">
+        <x:v>Counts</x:v>
+      </x:c>
+      <x:c r="D6" s="7" t="str">
+        <x:v>A41:BB50</x:v>
+      </x:c>
+      <x:c r="E6" s="7" t="str">
+        <x:v>S3_AgeGroup</x:v>
+      </x:c>
+      <x:c r="F6" s="7" t="str">
+        <x:v>S3_AgeGroup: Age Group</x:v>
+      </x:c>
+      <x:c r="G6" s="7" t="str">
+        <x:v>S3_AgeGroup: Age Group</x:v>
+      </x:c>
+      <x:c r="H6" s="7" t="n">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="S3"/>
-      <x:c r="T3"/>
-      <x:c r="U3"/>
-      <x:c r="V3"/>
-      <x:c r="W3"/>
+      <x:c r="I6" s="7" t="str">
+        <x:v>43:44</x:v>
+      </x:c>
+      <x:c r="J6" s="7" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K6" s="7" t="str">
+        <x:v>46:50</x:v>
+      </x:c>
+      <x:c r="L6" s="7"/>
+      <x:c r="M6" s="7" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="N6" s="7" t="str">
+        <x:v>cross_tab</x:v>
+      </x:c>
+      <x:c r="O6" s="7" t="str">
+        <x:v>HK/TW</x:v>
+      </x:c>
+      <x:c r="P6" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q6" s="7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="R6" s="7" t="str">
+        <x:v>Initial; no sig in Counts</x:v>
+      </x:c>
+      <x:c r="S6" s="7" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="T6" s="7" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="U6" s="7" t="str">
+        <x:v>accepted</x:v>
+      </x:c>
+      <x:c r="V6" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W6" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="7" t="str">
+        <x:v>G002</x:v>
+      </x:c>
+      <x:c r="B7" s="7" t="str">
+        <x:v>G002_T05</x:v>
+      </x:c>
+      <x:c r="C7" s="7" t="str">
+        <x:v>Counts</x:v>
+      </x:c>
+      <x:c r="D7" s="7" t="str">
+        <x:v>A53:BB64</x:v>
+      </x:c>
+      <x:c r="E7" s="7" t="str">
+        <x:v>S4</x:v>
+      </x:c>
+      <x:c r="F7" s="7" t="str">
+        <x:v>S4: 請問您目前的工作狀況是？</x:v>
+      </x:c>
+      <x:c r="G7" s="7" t="str">
+        <x:v>S4: 請問您目前的工作狀況是？</x:v>
+      </x:c>
+      <x:c r="H7" s="7" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="I7" s="7" t="str">
+        <x:v>55:56</x:v>
+      </x:c>
+      <x:c r="J7" s="7" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="K7" s="7" t="str">
+        <x:v>58:64</x:v>
+      </x:c>
+      <x:c r="L7" s="7"/>
+      <x:c r="M7" s="7" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="N7" s="7" t="str">
+        <x:v>cross_tab</x:v>
+      </x:c>
+      <x:c r="O7" s="7" t="str">
+        <x:v>HK/TW</x:v>
+      </x:c>
+      <x:c r="P7" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q7" s="7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="R7" s="7" t="str">
+        <x:v>Initial; no sig in Counts</x:v>
+      </x:c>
+      <x:c r="S7" s="7" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="T7" s="7" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="U7" s="7" t="str">
+        <x:v>accepted</x:v>
+      </x:c>
+      <x:c r="V7" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W7" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="7" t="str">
+        <x:v>G002</x:v>
+      </x:c>
+      <x:c r="B8" s="7" t="str">
+        <x:v>G002_T06</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="str">
+        <x:v>Counts</x:v>
+      </x:c>
+      <x:c r="D8" s="7" t="str">
+        <x:v>A67:BB79</x:v>
+      </x:c>
+      <x:c r="E8" s="7" t="str">
+        <x:v>S5</x:v>
+      </x:c>
+      <x:c r="F8" s="7" t="str">
+        <x:v>S5: 請問您目前的學歷是？</x:v>
+      </x:c>
+      <x:c r="G8" s="7" t="str">
+        <x:v>S5: 請問您目前的學歷是？</x:v>
+      </x:c>
+      <x:c r="H8" s="7" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="I8" s="7" t="str">
+        <x:v>69:70</x:v>
+      </x:c>
+      <x:c r="J8" s="7" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="K8" s="7" t="str">
+        <x:v>72:79</x:v>
+      </x:c>
+      <x:c r="L8" s="7"/>
+      <x:c r="M8" s="7" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="N8" s="7" t="str">
+        <x:v>cross_tab</x:v>
+      </x:c>
+      <x:c r="O8" s="7" t="str">
+        <x:v>HK/TW</x:v>
+      </x:c>
+      <x:c r="P8" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q8" s="7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="R8" s="7" t="str">
+        <x:v>Initial; no sig in Counts</x:v>
+      </x:c>
+      <x:c r="S8" s="7" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="T8" s="7" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="U8" s="7" t="str">
+        <x:v>accepted</x:v>
+      </x:c>
+      <x:c r="V8" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W8" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="7" t="str">
+        <x:v>G002</x:v>
+      </x:c>
+      <x:c r="B9" s="7" t="str">
+        <x:v>G002_T07</x:v>
+      </x:c>
+      <x:c r="C9" s="7" t="str">
+        <x:v>Counts</x:v>
+      </x:c>
+      <x:c r="D9" s="7" t="str">
+        <x:v>A82:BB93</x:v>
+      </x:c>
+      <x:c r="E9" s="7" t="str">
+        <x:v>S6</x:v>
+      </x:c>
+      <x:c r="F9" s="7" t="str">
+        <x:v>S6: 請問您本人或家人朋友中，有在以下地方工作嗎？</x:v>
+      </x:c>
+      <x:c r="G9" s="7" t="str">
+        <x:v>S6: 請問您本人或家人朋友中，有在以下地方工作嗎？</x:v>
+      </x:c>
+      <x:c r="H9" s="7" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="I9" s="7" t="str">
+        <x:v>84:85</x:v>
+      </x:c>
+      <x:c r="J9" s="7" t="n">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="K9" s="7" t="str">
+        <x:v>87:93</x:v>
+      </x:c>
+      <x:c r="L9" s="7"/>
+      <x:c r="M9" s="7" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="N9" s="7" t="str">
+        <x:v>cross_tab</x:v>
+      </x:c>
+      <x:c r="O9" s="7" t="str">
+        <x:v>HK/TW</x:v>
+      </x:c>
+      <x:c r="P9" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q9" s="7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="R9" s="7" t="str">
+        <x:v>Initial; no sig in Counts</x:v>
+      </x:c>
+      <x:c r="S9" s="7" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="T9" s="7" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="U9" s="7" t="str">
+        <x:v>accepted</x:v>
+      </x:c>
+      <x:c r="V9" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W9" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="7" t="str">
+        <x:v>G002</x:v>
+      </x:c>
+      <x:c r="B10" s="7" t="str">
+        <x:v>G002_T08</x:v>
+      </x:c>
+      <x:c r="C10" s="7" t="str">
+        <x:v>Counts</x:v>
+      </x:c>
+      <x:c r="D10" s="7" t="str">
+        <x:v>A96:BB108</x:v>
+      </x:c>
+      <x:c r="E10" s="7" t="str">
+        <x:v>S7</x:v>
+      </x:c>
+      <x:c r="F10" s="7" t="str">
+        <x:v>S7: 請問過去6個月，您有沒有参加過以下訪問或研究呢？</x:v>
+      </x:c>
+      <x:c r="G10" s="7" t="str">
+        <x:v>S7: 請問過去6個月，您有沒有参加過以下訪問或研究呢？</x:v>
+      </x:c>
+      <x:c r="H10" s="7" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="I10" s="7" t="str">
+        <x:v>98:99</x:v>
+      </x:c>
+      <x:c r="J10" s="7" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K10" s="7" t="str">
+        <x:v>101:108</x:v>
+      </x:c>
+      <x:c r="L10" s="7"/>
+      <x:c r="M10" s="7" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="N10" s="7" t="str">
+        <x:v>cross_tab</x:v>
+      </x:c>
+      <x:c r="O10" s="7" t="str">
+        <x:v>HK/TW</x:v>
+      </x:c>
+      <x:c r="P10" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q10" s="7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="R10" s="7" t="str">
+        <x:v>Initial; no sig in Counts</x:v>
+      </x:c>
+      <x:c r="S10" s="7" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="T10" s="7" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="U10" s="7" t="str">
+        <x:v>accepted</x:v>
+      </x:c>
+      <x:c r="V10" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W10" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="7" t="str">
+        <x:v>G002</x:v>
+      </x:c>
+      <x:c r="B11" s="7" t="str">
+        <x:v>G002_T09</x:v>
+      </x:c>
+      <x:c r="C11" s="7" t="str">
+        <x:v>Counts</x:v>
+      </x:c>
+      <x:c r="D11" s="7" t="str">
+        <x:v>A111:BB119</x:v>
+      </x:c>
+      <x:c r="E11" s="7" t="str">
+        <x:v>S8</x:v>
+      </x:c>
+      <x:c r="F11" s="7" t="str">
+        <x:v>S8: 請問您目前的個人狀態是？</x:v>
+      </x:c>
+      <x:c r="G11" s="7" t="str">
+        <x:v>S8: 請問您目前的個人狀態是？</x:v>
+      </x:c>
+      <x:c r="H11" s="7" t="n">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="I11" s="7" t="str">
+        <x:v>113:114</x:v>
+      </x:c>
+      <x:c r="J11" s="7" t="n">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="K11" s="7" t="str">
+        <x:v>116:119</x:v>
+      </x:c>
+      <x:c r="L11" s="7"/>
+      <x:c r="M11" s="7" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="N11" s="7" t="str">
+        <x:v>cross_tab</x:v>
+      </x:c>
+      <x:c r="O11" s="7" t="str">
+        <x:v>HK/TW</x:v>
+      </x:c>
+      <x:c r="P11" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q11" s="7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="R11" s="7" t="str">
+        <x:v>Initial; no sig in Counts</x:v>
+      </x:c>
+      <x:c r="S11" s="7" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="T11" s="7" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="U11" s="7" t="str">
+        <x:v>accepted</x:v>
+      </x:c>
+      <x:c r="V11" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W11" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="7" t="str">
+        <x:v>G002</x:v>
+      </x:c>
+      <x:c r="B12" s="7" t="str">
+        <x:v>G002_T10</x:v>
+      </x:c>
+      <x:c r="C12" s="7" t="str">
+        <x:v>Counts</x:v>
+      </x:c>
+      <x:c r="D12" s="7" t="str">
+        <x:v>A122:BB130</x:v>
+      </x:c>
+      <x:c r="E12" s="7" t="str">
+        <x:v>S9</x:v>
+      </x:c>
+      <x:c r="F12" s="7" t="str">
+        <x:v>S9: 請問您目前的孕產狀態是？
+請問以下哪個最切合您目前的狀態？</x:v>
+      </x:c>
+      <x:c r="G12" s="7" t="str">
+        <x:v>S9: 請問您目前的孕產狀態是？
+請問以下哪個最切合您目前的狀態？</x:v>
+      </x:c>
+      <x:c r="H12" s="7" t="n">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="I12" s="7" t="str">
+        <x:v>124:125</x:v>
+      </x:c>
+      <x:c r="J12" s="7" t="n">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="K12" s="7" t="str">
+        <x:v>127:130</x:v>
+      </x:c>
+      <x:c r="L12" s="7"/>
+      <x:c r="M12" s="7" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="N12" s="7" t="str">
+        <x:v>cross_tab</x:v>
+      </x:c>
+      <x:c r="O12" s="7" t="str">
+        <x:v>HK/TW</x:v>
+      </x:c>
+      <x:c r="P12" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q12" s="7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="R12" s="7" t="str">
+        <x:v>Initial; no sig in Counts</x:v>
+      </x:c>
+      <x:c r="S12" s="7" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="T12" s="7" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="U12" s="7" t="str">
+        <x:v>accepted</x:v>
+      </x:c>
+      <x:c r="V12" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W12" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="7" t="str">
+        <x:v>G003</x:v>
+      </x:c>
+      <x:c r="B13" s="7" t="str">
+        <x:v>G003_T01</x:v>
+      </x:c>
+      <x:c r="C13" s="7" t="str">
+        <x:v>ban1%N</x:v>
+      </x:c>
+      <x:c r="D13" s="7" t="str">
+        <x:v>A2:P22</x:v>
+      </x:c>
+      <x:c r="E13" s="7" t="str">
+        <x:v>S1b</x:v>
+      </x:c>
+      <x:c r="F13" s="7" t="str">
+        <x:v>S1b.Age</x:v>
+      </x:c>
+      <x:c r="G13" s="7" t="str">
+        <x:v>S1b.Age</x:v>
+      </x:c>
+      <x:c r="H13" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I13" s="7" t="str">
+        <x:v>5,7</x:v>
+      </x:c>
+      <x:c r="J13" s="7" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K13" s="7" t="str">
+        <x:v>10:19</x:v>
+      </x:c>
+      <x:c r="L13" s="7" t="str">
+        <x:v>21:22</x:v>
+      </x:c>
+      <x:c r="M13" s="7" t="str">
+        <x:v>combined</x:v>
+      </x:c>
+      <x:c r="N13" s="7" t="str">
+        <x:v>cross_tab</x:v>
+      </x:c>
+      <x:c r="O13" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P13" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q13" s="7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="R13" s="7" t="str">
+        <x:v>Initial; Count/% alternate; Sigma separate</x:v>
+      </x:c>
+      <x:c r="S13" s="7" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="T13" s="7" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="U13" s="7" t="str">
+        <x:v>accepted</x:v>
+      </x:c>
+      <x:c r="V13" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W13" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="7" t="str">
+        <x:v>G003</x:v>
+      </x:c>
+      <x:c r="B14" s="7" t="str">
+        <x:v>G003_T02</x:v>
+      </x:c>
+      <x:c r="C14" s="7" t="str">
+        <x:v>ban1%N</x:v>
+      </x:c>
+      <x:c r="D14" s="7" t="str">
+        <x:v>A25:P41</x:v>
+      </x:c>
+      <x:c r="E14" s="7" t="str">
+        <x:v>S2</x:v>
+      </x:c>
+      <x:c r="F14" s="7" t="str">
+        <x:v>S2.Gender</x:v>
+      </x:c>
+      <x:c r="G14" s="7" t="str">
+        <x:v>S2.Gender</x:v>
+      </x:c>
+      <x:c r="H14" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I14" s="7" t="str">
+        <x:v>28,30</x:v>
+      </x:c>
+      <x:c r="J14" s="7" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K14" s="7" t="str">
+        <x:v>33:38</x:v>
+      </x:c>
+      <x:c r="L14" s="7" t="str">
+        <x:v>40:41</x:v>
+      </x:c>
+      <x:c r="M14" s="7" t="str">
+        <x:v>combined</x:v>
+      </x:c>
+      <x:c r="N14" s="7" t="str">
+        <x:v>cross_tab</x:v>
+      </x:c>
+      <x:c r="O14" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P14" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q14" s="7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="R14" s="7" t="str">
+        <x:v>Initial; Count/% alternate; Sigma separate</x:v>
+      </x:c>
+      <x:c r="S14" s="7" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="T14" s="7" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="U14" s="7" t="str">
+        <x:v>accepted</x:v>
+      </x:c>
+      <x:c r="V14" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W14" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="7" t="str">
+        <x:v>G003</x:v>
+      </x:c>
+      <x:c r="B15" s="7" t="str">
+        <x:v>G003_T03</x:v>
+      </x:c>
+      <x:c r="C15" s="7" t="str">
+        <x:v>ban1%N</x:v>
+      </x:c>
+      <x:c r="D15" s="7" t="str">
+        <x:v>A44:P94</x:v>
+      </x:c>
+      <x:c r="E15" s="7" t="str">
+        <x:v>S3</x:v>
+      </x:c>
+      <x:c r="F15" s="7" t="str">
+        <x:v>S3.BMI score</x:v>
+      </x:c>
+      <x:c r="G15" s="7" t="str">
+        <x:v>S3.BMI score</x:v>
+      </x:c>
+      <x:c r="H15" s="7" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="I15" s="7" t="str">
+        <x:v>47,49</x:v>
+      </x:c>
+      <x:c r="J15" s="7" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K15" s="7" t="str">
+        <x:v>52:91</x:v>
+      </x:c>
+      <x:c r="L15" s="7" t="str">
+        <x:v>93:94</x:v>
+      </x:c>
+      <x:c r="M15" s="7" t="str">
+        <x:v>combined</x:v>
+      </x:c>
+      <x:c r="N15" s="7" t="str">
+        <x:v>cross_tab</x:v>
+      </x:c>
+      <x:c r="O15" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P15" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q15" s="7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="R15" s="7" t="str">
+        <x:v>Initial; Count/% alternate; Sigma separate</x:v>
+      </x:c>
+      <x:c r="S15" s="7" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="T15" s="7" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="U15" s="7" t="str">
+        <x:v>accepted</x:v>
+      </x:c>
+      <x:c r="V15" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W15" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="7" t="str">
+        <x:v>G003</x:v>
+      </x:c>
+      <x:c r="B16" s="7" t="str">
+        <x:v>G003_T04</x:v>
+      </x:c>
+      <x:c r="C16" s="7" t="str">
+        <x:v>ban1%N</x:v>
+      </x:c>
+      <x:c r="D16" s="7" t="str">
+        <x:v>A104:P146</x:v>
+      </x:c>
+      <x:c r="E16" s="7" t="str">
+        <x:v>S4a</x:v>
+      </x:c>
+      <x:c r="F16" s="7" t="str">
+        <x:v>S4a.Comorbidities</x:v>
+      </x:c>
+      <x:c r="G16" s="7" t="str">
+        <x:v>S4a.Comorbidities</x:v>
+      </x:c>
+      <x:c r="H16" s="7" t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="I16" s="7" t="str">
+        <x:v>107,109</x:v>
+      </x:c>
+      <x:c r="J16" s="7" t="n">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="K16" s="7" t="str">
+        <x:v>112:143</x:v>
+      </x:c>
+      <x:c r="L16" s="7" t="str">
+        <x:v>145:146</x:v>
+      </x:c>
+      <x:c r="M16" s="7" t="str">
+        <x:v>combined</x:v>
+      </x:c>
+      <x:c r="N16" s="7" t="str">
+        <x:v>cross_tab</x:v>
+      </x:c>
+      <x:c r="O16" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P16" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q16" s="7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="R16" s="7" t="str">
+        <x:v>Initial; Count/% alternate; Sigma separate</x:v>
+      </x:c>
+      <x:c r="S16" s="7" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="T16" s="7" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="U16" s="7" t="str">
+        <x:v>accepted</x:v>
+      </x:c>
+      <x:c r="V16" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W16" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="7" t="str">
+        <x:v>G003</x:v>
+      </x:c>
+      <x:c r="B17" s="7" t="str">
+        <x:v>G003_T05</x:v>
+      </x:c>
+      <x:c r="C17" s="7" t="str">
+        <x:v>ban1%N</x:v>
+      </x:c>
+      <x:c r="D17" s="7" t="str">
+        <x:v>A149:P191</x:v>
+      </x:c>
+      <x:c r="E17" s="7" t="str">
+        <x:v>S4b</x:v>
+      </x:c>
+      <x:c r="F17" s="7" t="str">
+        <x:v>S4b.Family history</x:v>
+      </x:c>
+      <x:c r="G17" s="7" t="str">
+        <x:v>S4b.Family history</x:v>
+      </x:c>
+      <x:c r="H17" s="7" t="n">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="I17" s="7" t="str">
+        <x:v>152,154</x:v>
+      </x:c>
+      <x:c r="J17" s="7" t="n">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="K17" s="7" t="str">
+        <x:v>157:188</x:v>
+      </x:c>
+      <x:c r="L17" s="7" t="str">
+        <x:v>190:191</x:v>
+      </x:c>
+      <x:c r="M17" s="7" t="str">
+        <x:v>combined</x:v>
+      </x:c>
+      <x:c r="N17" s="7" t="str">
+        <x:v>cross_tab</x:v>
+      </x:c>
+      <x:c r="O17" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P17" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q17" s="7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="R17" s="7" t="str">
+        <x:v>Initial; Count/% alternate; Sigma separate</x:v>
+      </x:c>
+      <x:c r="S17" s="7" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="T17" s="7" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="U17" s="7" t="str">
+        <x:v>accepted</x:v>
+      </x:c>
+      <x:c r="V17" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W17" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="7" t="str">
+        <x:v>G003</x:v>
+      </x:c>
+      <x:c r="B18" s="7" t="str">
+        <x:v>G003_T06</x:v>
+      </x:c>
+      <x:c r="C18" s="7" t="str">
+        <x:v>ban1%N</x:v>
+      </x:c>
+      <x:c r="D18" s="7" t="str">
+        <x:v>A194:P224</x:v>
+      </x:c>
+      <x:c r="E18" s="7" t="str">
+        <x:v>S6</x:v>
+      </x:c>
+      <x:c r="F18" s="7" t="str">
+        <x:v>S6.Obesity treatment in P12M</x:v>
+      </x:c>
+      <x:c r="G18" s="7" t="str">
+        <x:v>S6.Obesity treatment in P12M</x:v>
+      </x:c>
+      <x:c r="H18" s="7" t="n">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="I18" s="7" t="str">
+        <x:v>197,199</x:v>
+      </x:c>
+      <x:c r="J18" s="7" t="n">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="K18" s="7" t="str">
+        <x:v>202:221</x:v>
+      </x:c>
+      <x:c r="L18" s="7" t="str">
+        <x:v>223:224</x:v>
+      </x:c>
+      <x:c r="M18" s="7" t="str">
+        <x:v>combined</x:v>
+      </x:c>
+      <x:c r="N18" s="7" t="str">
+        <x:v>cross_tab</x:v>
+      </x:c>
+      <x:c r="O18" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P18" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q18" s="7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="R18" s="7" t="str">
+        <x:v>Initial; Count/% alternate; Sigma separate</x:v>
+      </x:c>
+      <x:c r="S18" s="7" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="T18" s="7" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="U18" s="7" t="str">
+        <x:v>accepted</x:v>
+      </x:c>
+      <x:c r="V18" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W18" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="7" t="str">
+        <x:v>G003</x:v>
+      </x:c>
+      <x:c r="B19" s="7" t="str">
+        <x:v>G003_T07</x:v>
+      </x:c>
+      <x:c r="C19" s="7" t="str">
+        <x:v>ban1%N</x:v>
+      </x:c>
+      <x:c r="D19" s="7" t="str">
+        <x:v>A227:P255</x:v>
+      </x:c>
+      <x:c r="E19" s="7" t="str">
+        <x:v>S8</x:v>
+      </x:c>
+      <x:c r="F19" s="7" t="str">
+        <x:v>S8.Prescription obesity treatment</x:v>
+      </x:c>
+      <x:c r="G19" s="7" t="str">
+        <x:v>S8.Prescription obesity treatment</x:v>
+      </x:c>
+      <x:c r="H19" s="7" t="n">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="I19" s="7" t="str">
+        <x:v>230,232</x:v>
+      </x:c>
+      <x:c r="J19" s="7" t="n">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="K19" s="7" t="str">
+        <x:v>235:252</x:v>
+      </x:c>
+      <x:c r="L19" s="7" t="str">
+        <x:v>254:255</x:v>
+      </x:c>
+      <x:c r="M19" s="7" t="str">
+        <x:v>combined</x:v>
+      </x:c>
+      <x:c r="N19" s="7" t="str">
+        <x:v>cross_tab</x:v>
+      </x:c>
+      <x:c r="O19" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P19" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q19" s="7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="R19" s="7" t="str">
+        <x:v>Initial; Count/% alternate; Sigma separate</x:v>
+      </x:c>
+      <x:c r="S19" s="7" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="T19" s="7" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="U19" s="7" t="str">
+        <x:v>accepted</x:v>
+      </x:c>
+      <x:c r="V19" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W19" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="7" t="str">
+        <x:v>G003</x:v>
+      </x:c>
+      <x:c r="B20" s="7" t="str">
+        <x:v>G003_T08</x:v>
+      </x:c>
+      <x:c r="C20" s="7" t="str">
+        <x:v>ban1%N</x:v>
+      </x:c>
+      <x:c r="D20" s="7" t="str">
+        <x:v>A258:P276</x:v>
+      </x:c>
+      <x:c r="E20" s="7" t="str">
+        <x:v>S9</x:v>
+      </x:c>
+      <x:c r="F20" s="7" t="str">
+        <x:v>S9.Race</x:v>
+      </x:c>
+      <x:c r="G20" s="7" t="str">
+        <x:v>S9.Race</x:v>
+      </x:c>
+      <x:c r="H20" s="7" t="n">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="I20" s="7" t="str">
+        <x:v>261,263</x:v>
+      </x:c>
+      <x:c r="J20" s="7" t="n">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="K20" s="7" t="str">
+        <x:v>266:273</x:v>
+      </x:c>
+      <x:c r="L20" s="7" t="str">
+        <x:v>275:276</x:v>
+      </x:c>
+      <x:c r="M20" s="7" t="str">
+        <x:v>combined</x:v>
+      </x:c>
+      <x:c r="N20" s="7" t="str">
+        <x:v>cross_tab</x:v>
+      </x:c>
+      <x:c r="O20" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P20" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q20" s="7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="R20" s="7" t="str">
+        <x:v>Initial; Count/% alternate; Sigma separate</x:v>
+      </x:c>
+      <x:c r="S20" s="7" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="T20" s="7" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="U20" s="7" t="str">
+        <x:v>accepted</x:v>
+      </x:c>
+      <x:c r="V20" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W20" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="7" t="str">
+        <x:v>G003</x:v>
+      </x:c>
+      <x:c r="B21" s="7" t="str">
+        <x:v>G003_T09</x:v>
+      </x:c>
+      <x:c r="C21" s="7" t="str">
+        <x:v>ban1%N</x:v>
+      </x:c>
+      <x:c r="D21" s="7" t="str">
+        <x:v>A279:P309</x:v>
+      </x:c>
+      <x:c r="E21" s="7" t="str">
+        <x:v>S10</x:v>
+      </x:c>
+      <x:c r="F21" s="7" t="str">
+        <x:v>S10.Occupation</x:v>
+      </x:c>
+      <x:c r="G21" s="7" t="str">
+        <x:v>S10.Occupation</x:v>
+      </x:c>
+      <x:c r="H21" s="7" t="n">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="I21" s="7" t="str">
+        <x:v>282,284</x:v>
+      </x:c>
+      <x:c r="J21" s="7" t="n">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="K21" s="7" t="str">
+        <x:v>287:306</x:v>
+      </x:c>
+      <x:c r="L21" s="7" t="str">
+        <x:v>308:309</x:v>
+      </x:c>
+      <x:c r="M21" s="7" t="str">
+        <x:v>combined</x:v>
+      </x:c>
+      <x:c r="N21" s="7" t="str">
+        <x:v>cross_tab</x:v>
+      </x:c>
+      <x:c r="O21" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P21" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q21" s="7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="R21" s="7" t="str">
+        <x:v>Initial; Count/% alternate; Sigma separate</x:v>
+      </x:c>
+      <x:c r="S21" s="7" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="T21" s="7" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="U21" s="7" t="str">
+        <x:v>accepted</x:v>
+      </x:c>
+      <x:c r="V21" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W21" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="7" t="str">
+        <x:v>G003</x:v>
+      </x:c>
+      <x:c r="B22" s="7" t="str">
+        <x:v>G003_T10</x:v>
+      </x:c>
+      <x:c r="C22" s="7" t="str">
+        <x:v>ban1%N</x:v>
+      </x:c>
+      <x:c r="D22" s="7" t="str">
+        <x:v>A312:P330</x:v>
+      </x:c>
+      <x:c r="E22" s="7" t="str">
+        <x:v>S11</x:v>
+      </x:c>
+      <x:c r="F22" s="7" t="str">
+        <x:v>S11.Payment</x:v>
+      </x:c>
+      <x:c r="G22" s="7" t="str">
+        <x:v>S11.Payment</x:v>
+      </x:c>
+      <x:c r="H22" s="7" t="n">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="I22" s="7" t="str">
+        <x:v>315,317</x:v>
+      </x:c>
+      <x:c r="J22" s="7" t="n">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="K22" s="7" t="str">
+        <x:v>320:327</x:v>
+      </x:c>
+      <x:c r="L22" s="7" t="str">
+        <x:v>329:330</x:v>
+      </x:c>
+      <x:c r="M22" s="7" t="str">
+        <x:v>combined</x:v>
+      </x:c>
+      <x:c r="N22" s="7" t="str">
+        <x:v>cross_tab</x:v>
+      </x:c>
+      <x:c r="O22" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P22" s="7" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q22" s="7" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="R22" s="7" t="str">
+        <x:v>Initial; Count/% alternate; Sigma separate</x:v>
+      </x:c>
+      <x:c r="S22" s="7" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="T22" s="7" t="str">
+        <x:v>complete</x:v>
+      </x:c>
+      <x:c r="U22" s="7" t="str">
+        <x:v>accepted</x:v>
+      </x:c>
+      <x:c r="V22" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W22" s="9" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -829,13 +2301,13 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="B1" t="s">
+      <x:c r="C1" t="s">
         <x:v>43</x:v>
-      </x:c>
-      <x:c r="C1" t="s">
-        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -843,7 +2315,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B2" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C2" t="s">
         <x:v>29</x:v>
@@ -851,68 +2323,68 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B3" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B3" t="s">
+      <x:c r="C3" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="C3" t="s">
-        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B4" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B4" t="s">
+      <x:c r="C4" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="C4" t="s">
-        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B5" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B5" t="s">
+      <x:c r="C5" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="C5" t="s">
-        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B6" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B6" t="s">
+      <x:c r="C6" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="C6" t="s">
-        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B7" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B7" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="C7" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B8" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B8" t="s">
+      <x:c r="C8" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="C8" t="s">
-        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="14.5"/>
@@ -921,19 +2393,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="17">
@@ -941,16 +2413,16 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C11" s="2" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D11" s="2" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="C11" s="2" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D11" s="2" t="s">
-        <x:v>64</x:v>
-      </x:c>
       <x:c r="E11" s="2" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F11" s="2"/>
     </x:row>
@@ -959,19 +2431,19 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B12" s="2" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C12" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D12" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E12" s="2" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F12" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="17">
@@ -979,19 +2451,19 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B13" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D13" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E13" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F13" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1002,201 +2474,1711 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="14"/>
+  <x:cols>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="13" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1" ht="50">
-      <x:c r="A1" s="1" t="s">
+      <x:c r="A1" s="10" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B1" s="10" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="B1" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="C1" s="7"/>
+      <x:c r="D1" s="10" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="E1" s="10" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F1" s="10" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="G1" s="10" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="H1" s="10" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="I1" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="J1" s="10" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="I1" s="1" t="s">
+    </x:row>
+    <x:row r="2" ht="33.5">
+      <x:c r="A2" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B2" s="11" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C2" s="7"/>
+      <x:c r="D2" s="11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E2" s="11" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="F2" s="11" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G2" s="11" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H2" s="11">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="I2" s="11" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="J2" s="11"/>
+    </x:row>
+    <x:row r="3" ht="33.5">
+      <x:c r="A3" s="11" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C3" s="7"/>
+      <x:c r="D3" s="11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E3" s="11" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F3" s="11" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G3" s="11" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H3" s="12">
+        <x:v>0.62</x:v>
+      </x:c>
+      <x:c r="I3" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="J3" s="11"/>
+    </x:row>
+    <x:row r="4" ht="50">
+      <x:c r="A4" s="11" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B4" s="11" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C4" s="7"/>
+      <x:c r="D4" s="11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E4" s="11" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F4" s="11" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G4" s="11" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H4" s="12">
+        <x:v>0.68</x:v>
+      </x:c>
+      <x:c r="I4" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="J4" s="11" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="50">
+      <x:c r="A5" s="11" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C5" s="7"/>
+      <x:c r="D5" s="11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F5" s="11" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G5" s="11" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="H5" s="12">
+        <x:v>0.56000000000000005</x:v>
+      </x:c>
+      <x:c r="I5" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="J5" s="11"/>
+    </x:row>
+    <x:row r="6" ht="50">
+      <x:c r="A6" s="11" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C6" s="7"/>
+      <x:c r="D6" s="7"/>
+      <x:c r="E6" s="7"/>
+      <x:c r="F6" s="7"/>
+      <x:c r="G6" s="7"/>
+      <x:c r="H6" s="7"/>
+      <x:c r="I6" s="7"/>
+      <x:c r="J6" s="7"/>
+    </x:row>
+    <x:row r="7" ht="50">
+      <x:c r="A7" s="11" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B7" s="11" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C7" s="7"/>
+      <x:c r="D7" s="7"/>
+      <x:c r="E7" s="7"/>
+      <x:c r="F7" s="7"/>
+      <x:c r="G7" s="7"/>
+      <x:c r="H7" s="7"/>
+      <x:c r="I7" s="7"/>
+      <x:c r="J7" s="7"/>
+    </x:row>
+    <x:row r="8" ht="50">
+      <x:c r="A8" s="11" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="J1" s="1" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="33.5">
-      <x:c r="A2" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B2" s="2" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D2" s="2" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E2" s="2" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="F2" s="2" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="G2" s="2" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="H2" s="2">
-        <x:v>600</x:v>
-      </x:c>
-      <x:c r="I2" s="2" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="J2" s="2"/>
-    </x:row>
-    <x:row r="3" ht="33.5">
-      <x:c r="A3" s="2" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="D3" s="2" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E3" s="2" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="F3" s="2" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="G3" s="2" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="H3" s="5">
-        <x:v>0.62</x:v>
-      </x:c>
-      <x:c r="I3" s="2" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="J3" s="2"/>
-    </x:row>
-    <x:row r="4" ht="50">
-      <x:c r="A4" s="2" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="B4" s="2" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D4" s="2" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E4" s="2" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F4" s="2" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="G4" s="2" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="H4" s="5">
-        <x:v>0.68</x:v>
-      </x:c>
-      <x:c r="I4" s="2" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="J4" s="2" t="s">
-        <x:v>63</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="50">
-      <x:c r="A5" s="2" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="B5" s="2" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D5" s="2" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E5" s="2" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="F5" s="2" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="G5" s="2" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="H5" s="5">
-        <x:v>0.56000000000000005</x:v>
-      </x:c>
-      <x:c r="I5" s="2" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="J5" s="2"/>
-    </x:row>
-    <x:row r="6" ht="50">
-      <x:c r="A6" s="2" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="B6" s="2" t="s">
+      <x:c r="B8" s="11" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C8" s="7"/>
+      <x:c r="D8" s="7"/>
+      <x:c r="E8" s="7"/>
+      <x:c r="F8" s="7"/>
+      <x:c r="G8" s="7"/>
+      <x:c r="H8" s="7"/>
+      <x:c r="I8" s="7"/>
+      <x:c r="J8" s="7"/>
+    </x:row>
+    <x:row r="9" ht="50">
+      <x:c r="A9" s="11" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B9" s="11" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C9" s="7"/>
+      <x:c r="D9" s="7"/>
+      <x:c r="E9" s="7"/>
+      <x:c r="F9" s="7"/>
+      <x:c r="G9" s="7"/>
+      <x:c r="H9" s="7"/>
+      <x:c r="I9" s="7"/>
+      <x:c r="J9" s="7"/>
+    </x:row>
+    <x:row r="10" ht="50">
+      <x:c r="A10" s="11" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B10" s="11" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C10" s="7"/>
+      <x:c r="D10" s="7"/>
+      <x:c r="E10" s="7"/>
+      <x:c r="F10" s="7"/>
+      <x:c r="G10" s="7"/>
+      <x:c r="H10" s="7"/>
+      <x:c r="I10" s="7"/>
+      <x:c r="J10" s="7"/>
+    </x:row>
+    <x:row r="11" ht="50">
+      <x:c r="A11" s="11" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B11" s="11" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C11" s="7"/>
+      <x:c r="D11" s="7"/>
+      <x:c r="E11" s="7"/>
+      <x:c r="F11" s="7"/>
+      <x:c r="G11" s="7"/>
+      <x:c r="H11" s="7"/>
+      <x:c r="I11" s="7"/>
+      <x:c r="J11" s="7"/>
+    </x:row>
+    <x:row r="12" ht="17">
+      <x:c r="A12" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B12" s="11" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C12" s="7"/>
+      <x:c r="D12" s="7"/>
+      <x:c r="E12" s="7"/>
+      <x:c r="F12" s="7"/>
+      <x:c r="G12" s="7"/>
+      <x:c r="H12" s="7"/>
+      <x:c r="I12" s="7"/>
+      <x:c r="J12" s="7"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="7"/>
+      <x:c r="B13" s="7"/>
+      <x:c r="C13" s="7"/>
+      <x:c r="D13" s="7" t="str">
+        <x:v>G002_T01</x:v>
+      </x:c>
+      <x:c r="E13" s="7" t="str">
+        <x:v>B16</x:v>
+      </x:c>
+      <x:c r="F13" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="G13" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="H13" s="7" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="I13" s="7" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="J13" s="7"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="7"/>
+      <x:c r="B14" s="7"/>
+      <x:c r="C14" s="7"/>
+      <x:c r="D14" s="7" t="str">
+        <x:v>G002_T01</x:v>
+      </x:c>
+      <x:c r="E14" s="7" t="str">
+        <x:v>B17</x:v>
+      </x:c>
+      <x:c r="F14" s="7" t="str">
+        <x:v>男</x:v>
+      </x:c>
+      <x:c r="G14" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="H14" s="7" t="n">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="I14" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J14" s="7"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="7"/>
+      <x:c r="B15" s="7"/>
+      <x:c r="C15" s="7"/>
+      <x:c r="D15" s="7" t="str">
+        <x:v>G002_T01</x:v>
+      </x:c>
+      <x:c r="E15" s="7" t="str">
+        <x:v>C17</x:v>
+      </x:c>
+      <x:c r="F15" s="7" t="str">
+        <x:v>男</x:v>
+      </x:c>
+      <x:c r="G15" s="7" t="str">
+        <x:v>Male</x:v>
+      </x:c>
+      <x:c r="H15" s="7" t="n">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="I15" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J15" s="7"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="7"/>
+      <x:c r="B16" s="7"/>
+      <x:c r="C16" s="7"/>
+      <x:c r="D16" s="7" t="str">
+        <x:v>G002_T02</x:v>
+      </x:c>
+      <x:c r="E16" s="7" t="str">
+        <x:v>B25</x:v>
+      </x:c>
+      <x:c r="F16" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="G16" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="H16" s="7" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="I16" s="7" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="J16" s="7"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="7"/>
+      <x:c r="B17" s="7"/>
+      <x:c r="C17" s="7"/>
+      <x:c r="D17" s="7" t="str">
+        <x:v>G002_T02</x:v>
+      </x:c>
+      <x:c r="E17" s="7" t="str">
+        <x:v>B26</x:v>
+      </x:c>
+      <x:c r="F17" s="7" t="str">
+        <x:v>港島</x:v>
+      </x:c>
+      <x:c r="G17" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="H17" s="7" t="n">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="I17" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J17" s="7"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="7"/>
+      <x:c r="B18" s="7"/>
+      <x:c r="C18" s="7"/>
+      <x:c r="D18" s="7" t="str">
+        <x:v>G002_T02</x:v>
+      </x:c>
+      <x:c r="E18" s="7" t="str">
+        <x:v>C26</x:v>
+      </x:c>
+      <x:c r="F18" s="7" t="str">
+        <x:v>港島</x:v>
+      </x:c>
+      <x:c r="G18" s="7" t="str">
+        <x:v>Male</x:v>
+      </x:c>
+      <x:c r="H18" s="7" t="n">
         <x:v>85</x:v>
       </x:c>
-    </x:row>
-    <x:row r="7" ht="50">
-      <x:c r="A7" s="2" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="B7" s="2" t="s">
-        <x:v>86</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="50">
-      <x:c r="A8" s="2" t="s">
+      <x:c r="I18" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J18" s="7"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="7"/>
+      <x:c r="B19" s="7"/>
+      <x:c r="C19" s="7"/>
+      <x:c r="D19" s="7" t="str">
+        <x:v>G002_T03</x:v>
+      </x:c>
+      <x:c r="E19" s="7" t="str">
+        <x:v>B35</x:v>
+      </x:c>
+      <x:c r="F19" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="G19" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="H19" s="7" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="I19" s="7" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="J19" s="7"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="7"/>
+      <x:c r="B20" s="7"/>
+      <x:c r="C20" s="7"/>
+      <x:c r="D20" s="7" t="str">
+        <x:v>G002_T03</x:v>
+      </x:c>
+      <x:c r="E20" s="7" t="str">
+        <x:v>B36</x:v>
+      </x:c>
+      <x:c r="F20" s="7" t="str">
+        <x:v>Mean</x:v>
+      </x:c>
+      <x:c r="G20" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="H20" s="7" t="n">
+        <x:v>36.716</x:v>
+      </x:c>
+      <x:c r="I20" s="7" t="str">
+        <x:v>Mean</x:v>
+      </x:c>
+      <x:c r="J20" s="7"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="7"/>
+      <x:c r="B21" s="7"/>
+      <x:c r="C21" s="7"/>
+      <x:c r="D21" s="7" t="str">
+        <x:v>G002_T03</x:v>
+      </x:c>
+      <x:c r="E21" s="7" t="str">
+        <x:v>C36</x:v>
+      </x:c>
+      <x:c r="F21" s="7" t="str">
+        <x:v>Mean</x:v>
+      </x:c>
+      <x:c r="G21" s="7" t="str">
+        <x:v>Male</x:v>
+      </x:c>
+      <x:c r="H21" s="7" t="n">
+        <x:v>37.0547</x:v>
+      </x:c>
+      <x:c r="I21" s="7" t="str">
+        <x:v>Mean</x:v>
+      </x:c>
+      <x:c r="J21" s="7"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="7"/>
+      <x:c r="B22" s="7"/>
+      <x:c r="C22" s="7"/>
+      <x:c r="D22" s="7" t="str">
+        <x:v>G002_T04</x:v>
+      </x:c>
+      <x:c r="E22" s="7" t="str">
+        <x:v>B45</x:v>
+      </x:c>
+      <x:c r="F22" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="G22" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="H22" s="7" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="I22" s="7" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="J22" s="7"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="7"/>
+      <x:c r="B23" s="7"/>
+      <x:c r="C23" s="7"/>
+      <x:c r="D23" s="7" t="str">
+        <x:v>G002_T04</x:v>
+      </x:c>
+      <x:c r="E23" s="7" t="str">
+        <x:v>B46</x:v>
+      </x:c>
+      <x:c r="F23" s="7" t="str">
+        <x:v>18-24</x:v>
+      </x:c>
+      <x:c r="G23" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="H23" s="7" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="I23" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J23" s="7"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="7"/>
+      <x:c r="B24" s="7"/>
+      <x:c r="C24" s="7"/>
+      <x:c r="D24" s="7" t="str">
+        <x:v>G002_T04</x:v>
+      </x:c>
+      <x:c r="E24" s="7" t="str">
+        <x:v>C46</x:v>
+      </x:c>
+      <x:c r="F24" s="7" t="str">
+        <x:v>18-24</x:v>
+      </x:c>
+      <x:c r="G24" s="7" t="str">
+        <x:v>Male</x:v>
+      </x:c>
+      <x:c r="H24" s="7" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="I24" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J24" s="7"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="7"/>
+      <x:c r="B25" s="7"/>
+      <x:c r="C25" s="7"/>
+      <x:c r="D25" s="7" t="str">
+        <x:v>G002_T05</x:v>
+      </x:c>
+      <x:c r="E25" s="7" t="str">
+        <x:v>B57</x:v>
+      </x:c>
+      <x:c r="F25" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="G25" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="H25" s="7" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="I25" s="7" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="J25" s="7"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="7"/>
+      <x:c r="B26" s="7"/>
+      <x:c r="C26" s="7"/>
+      <x:c r="D26" s="7" t="str">
+        <x:v>G002_T05</x:v>
+      </x:c>
+      <x:c r="E26" s="7" t="str">
+        <x:v>B58</x:v>
+      </x:c>
+      <x:c r="F26" s="7" t="str">
+        <x:v>在校學生</x:v>
+      </x:c>
+      <x:c r="G26" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="H26" s="7" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="I26" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J26" s="7"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="7"/>
+      <x:c r="B27" s="7"/>
+      <x:c r="C27" s="7"/>
+      <x:c r="D27" s="7" t="str">
+        <x:v>G002_T05</x:v>
+      </x:c>
+      <x:c r="E27" s="7" t="str">
+        <x:v>C58</x:v>
+      </x:c>
+      <x:c r="F27" s="7" t="str">
+        <x:v>在校學生</x:v>
+      </x:c>
+      <x:c r="G27" s="7" t="str">
+        <x:v>Male</x:v>
+      </x:c>
+      <x:c r="H27" s="7" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I27" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J27" s="7"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="7"/>
+      <x:c r="B28" s="7"/>
+      <x:c r="C28" s="7"/>
+      <x:c r="D28" s="7" t="str">
+        <x:v>G002_T06</x:v>
+      </x:c>
+      <x:c r="E28" s="7" t="str">
+        <x:v>B71</x:v>
+      </x:c>
+      <x:c r="F28" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="G28" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="H28" s="7" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="I28" s="7" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="J28" s="7"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="7"/>
+      <x:c r="B29" s="7"/>
+      <x:c r="C29" s="7"/>
+      <x:c r="D29" s="7" t="str">
+        <x:v>G002_T06</x:v>
+      </x:c>
+      <x:c r="E29" s="7" t="str">
+        <x:v>B72</x:v>
+      </x:c>
+      <x:c r="F29" s="7" t="str">
+        <x:v>小學</x:v>
+      </x:c>
+      <x:c r="G29" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="H29" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I29" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J29" s="7"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="7"/>
+      <x:c r="B30" s="7"/>
+      <x:c r="C30" s="7"/>
+      <x:c r="D30" s="7" t="str">
+        <x:v>G002_T06</x:v>
+      </x:c>
+      <x:c r="E30" s="7" t="str">
+        <x:v>C72</x:v>
+      </x:c>
+      <x:c r="F30" s="7" t="str">
+        <x:v>小學</x:v>
+      </x:c>
+      <x:c r="G30" s="7" t="str">
+        <x:v>Male</x:v>
+      </x:c>
+      <x:c r="H30" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I30" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J30" s="7"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="7"/>
+      <x:c r="B31" s="7"/>
+      <x:c r="C31" s="7"/>
+      <x:c r="D31" s="7" t="str">
+        <x:v>G002_T07</x:v>
+      </x:c>
+      <x:c r="E31" s="7" t="str">
+        <x:v>B86</x:v>
+      </x:c>
+      <x:c r="F31" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="G31" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="H31" s="7" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="I31" s="7" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="J31" s="7"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="7"/>
+      <x:c r="B32" s="7"/>
+      <x:c r="C32" s="7"/>
+      <x:c r="D32" s="7" t="str">
+        <x:v>G002_T07</x:v>
+      </x:c>
+      <x:c r="E32" s="7" t="str">
+        <x:v>B87</x:v>
+      </x:c>
+      <x:c r="F32" s="7" t="str">
+        <x:v>廣告公司</x:v>
+      </x:c>
+      <x:c r="G32" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="H32" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I32" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J32" s="7"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="7"/>
+      <x:c r="B33" s="7"/>
+      <x:c r="C33" s="7"/>
+      <x:c r="D33" s="7" t="str">
+        <x:v>G002_T07</x:v>
+      </x:c>
+      <x:c r="E33" s="7" t="str">
+        <x:v>C87</x:v>
+      </x:c>
+      <x:c r="F33" s="7" t="str">
+        <x:v>廣告公司</x:v>
+      </x:c>
+      <x:c r="G33" s="7" t="str">
+        <x:v>Male</x:v>
+      </x:c>
+      <x:c r="H33" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I33" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J33" s="7"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="7"/>
+      <x:c r="B34" s="7"/>
+      <x:c r="C34" s="7"/>
+      <x:c r="D34" s="7" t="str">
+        <x:v>G002_T08</x:v>
+      </x:c>
+      <x:c r="E34" s="7" t="str">
+        <x:v>B100</x:v>
+      </x:c>
+      <x:c r="F34" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="G34" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="H34" s="7" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="I34" s="7" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="J34" s="7"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="7"/>
+      <x:c r="B35" s="7"/>
+      <x:c r="C35" s="7"/>
+      <x:c r="D35" s="7" t="str">
+        <x:v>G002_T08</x:v>
+      </x:c>
+      <x:c r="E35" s="7" t="str">
+        <x:v>B101</x:v>
+      </x:c>
+      <x:c r="F35" s="7" t="str">
+        <x:v>婦女衛生護理</x:v>
+      </x:c>
+      <x:c r="G35" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="H35" s="7" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="I35" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J35" s="7"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="7"/>
+      <x:c r="B36" s="7"/>
+      <x:c r="C36" s="7"/>
+      <x:c r="D36" s="7" t="str">
+        <x:v>G002_T08</x:v>
+      </x:c>
+      <x:c r="E36" s="7" t="str">
+        <x:v>C101</x:v>
+      </x:c>
+      <x:c r="F36" s="7" t="str">
+        <x:v>婦女衛生護理</x:v>
+      </x:c>
+      <x:c r="G36" s="7" t="str">
+        <x:v>Male</x:v>
+      </x:c>
+      <x:c r="H36" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I36" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J36" s="7"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="7"/>
+      <x:c r="B37" s="7"/>
+      <x:c r="C37" s="7"/>
+      <x:c r="D37" s="7" t="str">
+        <x:v>G002_T09</x:v>
+      </x:c>
+      <x:c r="E37" s="7" t="str">
+        <x:v>B115</x:v>
+      </x:c>
+      <x:c r="F37" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="G37" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="H37" s="7" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="I37" s="7" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="J37" s="7"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="7"/>
+      <x:c r="B38" s="7"/>
+      <x:c r="C38" s="7"/>
+      <x:c r="D38" s="7" t="str">
+        <x:v>G002_T09</x:v>
+      </x:c>
+      <x:c r="E38" s="7" t="str">
+        <x:v>B116</x:v>
+      </x:c>
+      <x:c r="F38" s="7" t="str">
+        <x:v>未婚，沒有交往對象</x:v>
+      </x:c>
+      <x:c r="G38" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="H38" s="7" t="n">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="I38" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J38" s="7"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="7"/>
+      <x:c r="B39" s="7"/>
+      <x:c r="C39" s="7"/>
+      <x:c r="D39" s="7" t="str">
+        <x:v>G002_T09</x:v>
+      </x:c>
+      <x:c r="E39" s="7" t="str">
+        <x:v>C116</x:v>
+      </x:c>
+      <x:c r="F39" s="7" t="str">
+        <x:v>未婚，沒有交往對象</x:v>
+      </x:c>
+      <x:c r="G39" s="7" t="str">
+        <x:v>Male</x:v>
+      </x:c>
+      <x:c r="H39" s="7" t="n">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="I39" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J39" s="7"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="7"/>
+      <x:c r="B40" s="7"/>
+      <x:c r="C40" s="7"/>
+      <x:c r="D40" s="7" t="str">
+        <x:v>G002_T10</x:v>
+      </x:c>
+      <x:c r="E40" s="7" t="str">
+        <x:v>B126</x:v>
+      </x:c>
+      <x:c r="F40" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="G40" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="H40" s="7" t="n">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="I40" s="7" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="J40" s="7"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="7"/>
+      <x:c r="B41" s="7"/>
+      <x:c r="C41" s="7"/>
+      <x:c r="D41" s="7" t="str">
+        <x:v>G002_T10</x:v>
+      </x:c>
+      <x:c r="E41" s="7" t="str">
+        <x:v>B127</x:v>
+      </x:c>
+      <x:c r="F41" s="7" t="str">
+        <x:v>無孩</x:v>
+      </x:c>
+      <x:c r="G41" s="7" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="H41" s="7" t="n">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="I41" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J41" s="7"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="7"/>
+      <x:c r="B42" s="7"/>
+      <x:c r="C42" s="7"/>
+      <x:c r="D42" s="7" t="str">
+        <x:v>G002_T10</x:v>
+      </x:c>
+      <x:c r="E42" s="7" t="str">
+        <x:v>C127</x:v>
+      </x:c>
+      <x:c r="F42" s="7" t="str">
+        <x:v>無孩</x:v>
+      </x:c>
+      <x:c r="G42" s="7" t="str">
+        <x:v>Male</x:v>
+      </x:c>
+      <x:c r="H42" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I42" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J42" s="7"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="7"/>
+      <x:c r="B43" s="7"/>
+      <x:c r="C43" s="7"/>
+      <x:c r="D43" s="7" t="str">
+        <x:v>G003_T01</x:v>
+      </x:c>
+      <x:c r="E43" s="7" t="str">
+        <x:v>B9</x:v>
+      </x:c>
+      <x:c r="F43" s="7" t="str">
+        <x:v>Base: All Respondents</x:v>
+      </x:c>
+      <x:c r="G43" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H43" s="7" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B8" s="2" t="s">
-        <x:v>87</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="50">
-      <x:c r="A9" s="2" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="B9" s="2" t="s">
-        <x:v>89</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="50">
-      <x:c r="A10" s="2" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="B10" s="2" t="s">
-        <x:v>90</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="50">
-      <x:c r="A11" s="2" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="B11" s="2" t="s">
-        <x:v>92</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="17">
-      <x:c r="A12" s="2" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B12" s="2" t="s">
-        <x:v>93</x:v>
-      </x:c>
+      <x:c r="I43" s="7" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="J43" s="7"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="7"/>
+      <x:c r="B44" s="7"/>
+      <x:c r="C44" s="7"/>
+      <x:c r="D44" s="7" t="str">
+        <x:v>G003_T01</x:v>
+      </x:c>
+      <x:c r="E44" s="7" t="str">
+        <x:v>B10</x:v>
+      </x:c>
+      <x:c r="F44" s="7" t="str">
+        <x:v>&lt;18 years old</x:v>
+      </x:c>
+      <x:c r="G44" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H44" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I44" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J44" s="7"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="7"/>
+      <x:c r="B45" s="7"/>
+      <x:c r="C45" s="7"/>
+      <x:c r="D45" s="7" t="str">
+        <x:v>G003_T01</x:v>
+      </x:c>
+      <x:c r="E45" s="7" t="str">
+        <x:v>B11</x:v>
+      </x:c>
+      <x:c r="F45" s="7" t="str">
+        <x:v>&lt;18 years old</x:v>
+      </x:c>
+      <x:c r="G45" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H45" s="7" t="str">
+        <x:v>- </x:v>
+      </x:c>
+      <x:c r="I45" s="7" t="str">
+        <x:v>Percentage</x:v>
+      </x:c>
+      <x:c r="J45" s="7"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="7"/>
+      <x:c r="B46" s="7"/>
+      <x:c r="C46" s="7"/>
+      <x:c r="D46" s="7" t="str">
+        <x:v>G003_T02</x:v>
+      </x:c>
+      <x:c r="E46" s="7" t="str">
+        <x:v>B32</x:v>
+      </x:c>
+      <x:c r="F46" s="7" t="str">
+        <x:v>Base: All Respondents</x:v>
+      </x:c>
+      <x:c r="G46" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H46" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I46" s="7" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="J46" s="7"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="7"/>
+      <x:c r="B47" s="7"/>
+      <x:c r="C47" s="7"/>
+      <x:c r="D47" s="7" t="str">
+        <x:v>G003_T02</x:v>
+      </x:c>
+      <x:c r="E47" s="7" t="str">
+        <x:v>B33</x:v>
+      </x:c>
+      <x:c r="F47" s="7" t="str">
+        <x:v>Female</x:v>
+      </x:c>
+      <x:c r="G47" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H47" s="7" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I47" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J47" s="7"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="7"/>
+      <x:c r="B48" s="7"/>
+      <x:c r="C48" s="7"/>
+      <x:c r="D48" s="7" t="str">
+        <x:v>G003_T02</x:v>
+      </x:c>
+      <x:c r="E48" s="7" t="str">
+        <x:v>B34</x:v>
+      </x:c>
+      <x:c r="F48" s="7" t="str">
+        <x:v>Female</x:v>
+      </x:c>
+      <x:c r="G48" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H48" s="7" t="n">
+        <x:v>0.52</x:v>
+      </x:c>
+      <x:c r="I48" s="7" t="str">
+        <x:v>Percentage</x:v>
+      </x:c>
+      <x:c r="J48" s="7"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="7"/>
+      <x:c r="B49" s="7"/>
+      <x:c r="C49" s="7"/>
+      <x:c r="D49" s="7" t="str">
+        <x:v>G003_T03</x:v>
+      </x:c>
+      <x:c r="E49" s="7" t="str">
+        <x:v>B51</x:v>
+      </x:c>
+      <x:c r="F49" s="7" t="str">
+        <x:v>Base: All Respondents</x:v>
+      </x:c>
+      <x:c r="G49" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H49" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I49" s="7" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="J49" s="7"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="7"/>
+      <x:c r="B50" s="7"/>
+      <x:c r="C50" s="7"/>
+      <x:c r="D50" s="7" t="str">
+        <x:v>G003_T03</x:v>
+      </x:c>
+      <x:c r="E50" s="7" t="str">
+        <x:v>B52</x:v>
+      </x:c>
+      <x:c r="F50" s="7" t="str">
+        <x:v>27.6</x:v>
+      </x:c>
+      <x:c r="G50" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H50" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I50" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J50" s="7"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="7"/>
+      <x:c r="B51" s="7"/>
+      <x:c r="C51" s="7"/>
+      <x:c r="D51" s="7" t="str">
+        <x:v>G003_T03</x:v>
+      </x:c>
+      <x:c r="E51" s="7" t="str">
+        <x:v>B53</x:v>
+      </x:c>
+      <x:c r="F51" s="7" t="str">
+        <x:v>27.6</x:v>
+      </x:c>
+      <x:c r="G51" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H51" s="7" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="I51" s="7" t="str">
+        <x:v>Percentage</x:v>
+      </x:c>
+      <x:c r="J51" s="7"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="7"/>
+      <x:c r="B52" s="7"/>
+      <x:c r="C52" s="7"/>
+      <x:c r="D52" s="7" t="str">
+        <x:v>G003_T04</x:v>
+      </x:c>
+      <x:c r="E52" s="7" t="str">
+        <x:v>B111</x:v>
+      </x:c>
+      <x:c r="F52" s="7" t="str">
+        <x:v>Base: All Respondents</x:v>
+      </x:c>
+      <x:c r="G52" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H52" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I52" s="7" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="J52" s="7"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="7"/>
+      <x:c r="B53" s="7"/>
+      <x:c r="C53" s="7"/>
+      <x:c r="D53" s="7" t="str">
+        <x:v>G003_T04</x:v>
+      </x:c>
+      <x:c r="E53" s="7" t="str">
+        <x:v>B112</x:v>
+      </x:c>
+      <x:c r="F53" s="7" t="str">
+        <x:v>[Net]Cardio-renal-metabolic conditions</x:v>
+      </x:c>
+      <x:c r="G53" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H53" s="7" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I53" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J53" s="7"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="7"/>
+      <x:c r="B54" s="7"/>
+      <x:c r="C54" s="7"/>
+      <x:c r="D54" s="7" t="str">
+        <x:v>G003_T04</x:v>
+      </x:c>
+      <x:c r="E54" s="7" t="str">
+        <x:v>B113</x:v>
+      </x:c>
+      <x:c r="F54" s="7" t="str">
+        <x:v>[Net]Cardio-renal-metabolic conditions</x:v>
+      </x:c>
+      <x:c r="G54" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H54" s="7" t="n">
+        <x:v>0.28</x:v>
+      </x:c>
+      <x:c r="I54" s="7" t="str">
+        <x:v>Percentage</x:v>
+      </x:c>
+      <x:c r="J54" s="7"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="7"/>
+      <x:c r="B55" s="7"/>
+      <x:c r="C55" s="7"/>
+      <x:c r="D55" s="7" t="str">
+        <x:v>G003_T05</x:v>
+      </x:c>
+      <x:c r="E55" s="7" t="str">
+        <x:v>B156</x:v>
+      </x:c>
+      <x:c r="F55" s="7" t="str">
+        <x:v>Base: All Respondents</x:v>
+      </x:c>
+      <x:c r="G55" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H55" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I55" s="7" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="J55" s="7"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="7"/>
+      <x:c r="B56" s="7"/>
+      <x:c r="C56" s="7"/>
+      <x:c r="D56" s="7" t="str">
+        <x:v>G003_T05</x:v>
+      </x:c>
+      <x:c r="E56" s="7" t="str">
+        <x:v>B157</x:v>
+      </x:c>
+      <x:c r="F56" s="7" t="str">
+        <x:v>[Net]Cardio-renal-metabolic conditions</x:v>
+      </x:c>
+      <x:c r="G56" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H56" s="7" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="I56" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J56" s="7"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="7"/>
+      <x:c r="B57" s="7"/>
+      <x:c r="C57" s="7"/>
+      <x:c r="D57" s="7" t="str">
+        <x:v>G003_T05</x:v>
+      </x:c>
+      <x:c r="E57" s="7" t="str">
+        <x:v>B158</x:v>
+      </x:c>
+      <x:c r="F57" s="7" t="str">
+        <x:v>[Net]Cardio-renal-metabolic conditions</x:v>
+      </x:c>
+      <x:c r="G57" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H57" s="7" t="n">
+        <x:v>0.88</x:v>
+      </x:c>
+      <x:c r="I57" s="7" t="str">
+        <x:v>Percentage</x:v>
+      </x:c>
+      <x:c r="J57" s="7"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="7"/>
+      <x:c r="B58" s="7"/>
+      <x:c r="C58" s="7"/>
+      <x:c r="D58" s="7" t="str">
+        <x:v>G003_T06</x:v>
+      </x:c>
+      <x:c r="E58" s="7" t="str">
+        <x:v>B201</x:v>
+      </x:c>
+      <x:c r="F58" s="7" t="str">
+        <x:v>Base: All Respondents</x:v>
+      </x:c>
+      <x:c r="G58" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H58" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I58" s="7" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="J58" s="7"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="7"/>
+      <x:c r="B59" s="7"/>
+      <x:c r="C59" s="7"/>
+      <x:c r="D59" s="7" t="str">
+        <x:v>G003_T06</x:v>
+      </x:c>
+      <x:c r="E59" s="7" t="str">
+        <x:v>B202</x:v>
+      </x:c>
+      <x:c r="F59" s="7" t="str">
+        <x:v>Prescription weight loss medication (from a doctor)</x:v>
+      </x:c>
+      <x:c r="G59" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H59" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I59" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J59" s="7"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="7"/>
+      <x:c r="B60" s="7"/>
+      <x:c r="C60" s="7"/>
+      <x:c r="D60" s="7" t="str">
+        <x:v>G003_T06</x:v>
+      </x:c>
+      <x:c r="E60" s="7" t="str">
+        <x:v>B203</x:v>
+      </x:c>
+      <x:c r="F60" s="7" t="str">
+        <x:v>Prescription weight loss medication (from a doctor)</x:v>
+      </x:c>
+      <x:c r="G60" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H60" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I60" s="7" t="str">
+        <x:v>Percentage</x:v>
+      </x:c>
+      <x:c r="J60" s="7"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="7"/>
+      <x:c r="B61" s="7"/>
+      <x:c r="C61" s="7"/>
+      <x:c r="D61" s="7" t="str">
+        <x:v>G003_T07</x:v>
+      </x:c>
+      <x:c r="E61" s="7" t="str">
+        <x:v>B234</x:v>
+      </x:c>
+      <x:c r="F61" s="7" t="str">
+        <x:v>Base:All respondents coded 4 in S6</x:v>
+      </x:c>
+      <x:c r="G61" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H61" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I61" s="7" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="J61" s="7"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="7"/>
+      <x:c r="B62" s="7"/>
+      <x:c r="C62" s="7"/>
+      <x:c r="D62" s="7" t="str">
+        <x:v>G003_T07</x:v>
+      </x:c>
+      <x:c r="E62" s="7" t="str">
+        <x:v>B235</x:v>
+      </x:c>
+      <x:c r="F62" s="7" t="str">
+        <x:v>Xenical (orlistat)</x:v>
+      </x:c>
+      <x:c r="G62" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H62" s="7" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="I62" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J62" s="7"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="7"/>
+      <x:c r="B63" s="7"/>
+      <x:c r="C63" s="7"/>
+      <x:c r="D63" s="7" t="str">
+        <x:v>G003_T07</x:v>
+      </x:c>
+      <x:c r="E63" s="7" t="str">
+        <x:v>B236</x:v>
+      </x:c>
+      <x:c r="F63" s="7" t="str">
+        <x:v>Xenical (orlistat)</x:v>
+      </x:c>
+      <x:c r="G63" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H63" s="7" t="n">
+        <x:v>0.44</x:v>
+      </x:c>
+      <x:c r="I63" s="7" t="str">
+        <x:v>Percentage</x:v>
+      </x:c>
+      <x:c r="J63" s="7"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="7"/>
+      <x:c r="B64" s="7"/>
+      <x:c r="C64" s="7"/>
+      <x:c r="D64" s="7" t="str">
+        <x:v>G003_T08</x:v>
+      </x:c>
+      <x:c r="E64" s="7" t="str">
+        <x:v>B265</x:v>
+      </x:c>
+      <x:c r="F64" s="7" t="str">
+        <x:v>Base: All Respondents</x:v>
+      </x:c>
+      <x:c r="G64" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H64" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I64" s="7" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="J64" s="7"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="7"/>
+      <x:c r="B65" s="7"/>
+      <x:c r="C65" s="7"/>
+      <x:c r="D65" s="7" t="str">
+        <x:v>G003_T08</x:v>
+      </x:c>
+      <x:c r="E65" s="7" t="str">
+        <x:v>B266</x:v>
+      </x:c>
+      <x:c r="F65" s="7" t="str">
+        <x:v>Chinese</x:v>
+      </x:c>
+      <x:c r="G65" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H65" s="7" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I65" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J65" s="7"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="7"/>
+      <x:c r="B66" s="7"/>
+      <x:c r="C66" s="7"/>
+      <x:c r="D66" s="7" t="str">
+        <x:v>G003_T08</x:v>
+      </x:c>
+      <x:c r="E66" s="7" t="str">
+        <x:v>B267</x:v>
+      </x:c>
+      <x:c r="F66" s="7" t="str">
+        <x:v>Chinese</x:v>
+      </x:c>
+      <x:c r="G66" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H66" s="7" t="n">
+        <x:v>0.72</x:v>
+      </x:c>
+      <x:c r="I66" s="7" t="str">
+        <x:v>Percentage</x:v>
+      </x:c>
+      <x:c r="J66" s="7"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="7"/>
+      <x:c r="B67" s="7"/>
+      <x:c r="C67" s="7"/>
+      <x:c r="D67" s="7" t="str">
+        <x:v>G003_T09</x:v>
+      </x:c>
+      <x:c r="E67" s="7" t="str">
+        <x:v>B286</x:v>
+      </x:c>
+      <x:c r="F67" s="7" t="str">
+        <x:v>Base: All Respondents</x:v>
+      </x:c>
+      <x:c r="G67" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H67" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I67" s="7" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="J67" s="7"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="7"/>
+      <x:c r="B68" s="7"/>
+      <x:c r="C68" s="7"/>
+      <x:c r="D68" s="7" t="str">
+        <x:v>G003_T09</x:v>
+      </x:c>
+      <x:c r="E68" s="7" t="str">
+        <x:v>B287</x:v>
+      </x:c>
+      <x:c r="F68" s="7" t="str">
+        <x:v>Legislators, Senior Officials and Managers</x:v>
+      </x:c>
+      <x:c r="G68" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H68" s="7" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I68" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J68" s="7"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="7"/>
+      <x:c r="B69" s="7"/>
+      <x:c r="C69" s="7"/>
+      <x:c r="D69" s="7" t="str">
+        <x:v>G003_T09</x:v>
+      </x:c>
+      <x:c r="E69" s="7" t="str">
+        <x:v>B288</x:v>
+      </x:c>
+      <x:c r="F69" s="7" t="str">
+        <x:v>Legislators, Senior Officials and Managers</x:v>
+      </x:c>
+      <x:c r="G69" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H69" s="7" t="n">
+        <x:v>0.48</x:v>
+      </x:c>
+      <x:c r="I69" s="7" t="str">
+        <x:v>Percentage</x:v>
+      </x:c>
+      <x:c r="J69" s="7"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="7"/>
+      <x:c r="B70" s="7"/>
+      <x:c r="C70" s="7"/>
+      <x:c r="D70" s="7" t="str">
+        <x:v>G003_T10</x:v>
+      </x:c>
+      <x:c r="E70" s="7" t="str">
+        <x:v>B319</x:v>
+      </x:c>
+      <x:c r="F70" s="7" t="str">
+        <x:v>Base: All Respondents</x:v>
+      </x:c>
+      <x:c r="G70" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H70" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I70" s="7" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="J70" s="7"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="7"/>
+      <x:c r="B71" s="7"/>
+      <x:c r="C71" s="7"/>
+      <x:c r="D71" s="7" t="str">
+        <x:v>G003_T10</x:v>
+      </x:c>
+      <x:c r="E71" s="7" t="str">
+        <x:v>B320</x:v>
+      </x:c>
+      <x:c r="F71" s="7" t="str">
+        <x:v>I pay for it myself</x:v>
+      </x:c>
+      <x:c r="G71" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H71" s="7" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I71" s="7" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="J71" s="7"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="7"/>
+      <x:c r="B72" s="7"/>
+      <x:c r="C72" s="7"/>
+      <x:c r="D72" s="7" t="str">
+        <x:v>G003_T10</x:v>
+      </x:c>
+      <x:c r="E72" s="7" t="str">
+        <x:v>B321</x:v>
+      </x:c>
+      <x:c r="F72" s="7" t="str">
+        <x:v>I pay for it myself</x:v>
+      </x:c>
+      <x:c r="G72" s="7" t="str">
+        <x:v>Total Market</x:v>
+      </x:c>
+      <x:c r="H72" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I72" s="7" t="str">
+        <x:v>Percentage</x:v>
+      </x:c>
+      <x:c r="J72" s="7"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
